--- a/ig/DM-JUIN-2026/CodeSystem-tre-r376-type-evenement-administratif.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-tre-r376-type-evenement-administratif.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="143">
   <si>
     <t>Property</t>
   </si>
@@ -121,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>36</t>
+    <t>38</t>
   </si>
   <si>
     <t>Code</t>
@@ -253,6 +253,18 @@
     <t>1ère Autorisation d’activité - lieu d’exercice EGE</t>
   </si>
   <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>Création Activité Etablissement Psychiatrique</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>Suppression Activité Etablissement Psychiatrique</t>
+  </si>
+  <si>
     <t>010</t>
   </si>
   <si>
@@ -292,13 +304,13 @@
     <t>018</t>
   </si>
   <si>
+    <t>Transfert / cession d'une EGE</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
     <t>Transfert / reprise d'une EGE</t>
-  </si>
-  <si>
-    <t>019</t>
-  </si>
-  <si>
-    <t>Transfert / cession d'une EGE</t>
   </si>
   <si>
     <t>020</t>
@@ -862,7 +874,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1311,6 +1323,30 @@
       </c>
       <c r="D37" s="2"/>
     </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="D39" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
